--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/DataTypes.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/DataTypes.xlsx
@@ -146,7 +146,14 @@
     <x:numFmt numFmtId="2" formatCode="yyyy-MM-dd"/>
     <x:numFmt numFmtId="3" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="1">
+  <x:fonts count="2">
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/DataTypes.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/DataTypes.xlsx
@@ -540,8 +540,8 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="26.980625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="21.700625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="25.320625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="21.270625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:3">

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/DataTypes.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/DataTypes.xlsx
@@ -190,54 +190,54 @@
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="7">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="46" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="46" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
   <x:cellXfs count="7">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/DataTypes.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/DataTypes.xlsx
@@ -781,9 +781,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="38" spans="1:3">
-      <x:c r="B38" s="0" t="s"/>
-    </x:row>
+    <x:row r="38" spans="1:3"/>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/DataTypes.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/DataTypes.xlsx
@@ -142,9 +142,9 @@
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:numFmts count="4">
     <x:numFmt numFmtId="0" formatCode=""/>
-    <x:numFmt numFmtId="1" formatCode="@"/>
-    <x:numFmt numFmtId="2" formatCode="yyyy-MM-dd"/>
-    <x:numFmt numFmtId="3" formatCode="#,##0.00"/>
+    <x:numFmt numFmtId="165" formatCode="@"/>
+    <x:numFmt numFmtId="166" formatCode="yyyy-MM-dd"/>
+    <x:numFmt numFmtId="167" formatCode="#,##0.00"/>
   </x:numFmts>
   <x:fonts count="2">
     <x:font>
@@ -202,13 +202,13 @@
     <x:xf numFmtId="46" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
@@ -229,15 +229,15 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
